--- a/artfynd/A 20781-2023 artfynd.xlsx
+++ b/artfynd/A 20781-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20781-2023 artfynd.xlsx
+++ b/artfynd/A 20781-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>110489184</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -712,14 +707,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Landsvägsbodarna (Landsvägsbodarna), Ång</t>
+          <t>Landsvägsbodarna, Landsvägsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570810.1189360336</v>
+        <v>570810</v>
       </c>
       <c r="R2" t="n">
-        <v>7052052.915306641</v>
+        <v>7052052</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -788,15 +783,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110489268</v>
+        <v>110489321</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,28 +794,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570818.5072911305</v>
+        <v>570778</v>
       </c>
       <c r="R3" t="n">
-        <v>7052076.706756871</v>
+        <v>7052072</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,19 +852,14 @@
           <t>2023-06-30</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,15 +886,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110489321</v>
+        <v>110489328</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,35 +897,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Landsvägsbodarna 108 , Ång</t>
+          <t>Landsvägsbodarna, Landsvägsbodarna, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570778.9361859456</v>
+        <v>570742</v>
       </c>
       <c r="R4" t="n">
-        <v>7052071.370460165</v>
+        <v>7052079</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -976,27 +957,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2023-07-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +987,328 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>110489290</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Landsvägsbodarna 108 , Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570819</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7052077</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Erland Lindblad</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>110489248</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Landsvägsbodarna, Landsvägsbodarna, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>570837</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7052032</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-07-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110489268</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Landsvägsbodarna 108 , Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>570819</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7052077</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20781-2023 artfynd.xlsx
+++ b/artfynd/A 20781-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110489184</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110489321</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110489328</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1099,6 +1119,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110489290</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110489248</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,8 +1339,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110489268</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>